--- a/artfynd/A 32071-2026 artfynd.xlsx
+++ b/artfynd/A 32071-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141707</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141725</v>
       </c>
       <c r="B3" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32071-2026 artfynd.xlsx
+++ b/artfynd/A 32071-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141707</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32071-2026 artfynd.xlsx
+++ b/artfynd/A 32071-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136141707</v>
       </c>
       <c r="B2" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136141725</v>
       </c>
       <c r="B3" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136141666</v>
       </c>
       <c r="B4" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136141667</v>
       </c>
       <c r="B5" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136141746</v>
       </c>
       <c r="B6" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136141651</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136141748</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136141652</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136141661</v>
       </c>
       <c r="B10" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>136141663</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>136141665</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136141681</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>136141682</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>136141685</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>136141686</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>136141687</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>136141701</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>136141702</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>136141704</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136141705</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136141706</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>136141708</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>136141709</v>
       </c>
       <c r="B24" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>136141711</v>
       </c>
       <c r="B25" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136141712</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136141713</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136141715</v>
       </c>
       <c r="B28" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>136141719</v>
       </c>
       <c r="B29" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>136141720</v>
       </c>
       <c r="B30" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>136141722</v>
       </c>
       <c r="B31" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>136141723</v>
       </c>
       <c r="B32" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>136141726</v>
       </c>
       <c r="B33" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136141727</v>
       </c>
       <c r="B34" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>136141728</v>
       </c>
       <c r="B35" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>136141729</v>
       </c>
       <c r="B36" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136141731</v>
       </c>
       <c r="B37" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>136141732</v>
       </c>
       <c r="B38" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>136141733</v>
       </c>
       <c r="B39" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>136141734</v>
       </c>
       <c r="B40" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>136141736</v>
       </c>
       <c r="B41" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>136141738</v>
       </c>
       <c r="B42" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136141739</v>
       </c>
       <c r="B43" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>136141740</v>
       </c>
       <c r="B44" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>136141741</v>
       </c>
       <c r="B45" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>136141742</v>
       </c>
       <c r="B46" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>136141743</v>
       </c>
       <c r="B47" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>136141744</v>
       </c>
       <c r="B48" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>136141745</v>
       </c>
       <c r="B49" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>136141747</v>
       </c>
       <c r="B50" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>136141749</v>
       </c>
       <c r="B51" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>136141750</v>
       </c>
       <c r="B52" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136141751</v>
       </c>
       <c r="B53" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>136141753</v>
       </c>
       <c r="B54" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>136141754</v>
       </c>
       <c r="B55" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>136141756</v>
       </c>
       <c r="B56" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136141757</v>
       </c>
       <c r="B57" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>136141758</v>
       </c>
       <c r="B58" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>136141759</v>
       </c>
       <c r="B59" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>136141760</v>
       </c>
       <c r="B60" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>136141761</v>
       </c>
       <c r="B61" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>136141762</v>
       </c>
       <c r="B62" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>136141763</v>
       </c>
       <c r="B63" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>136141765</v>
       </c>
       <c r="B64" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>136141767</v>
       </c>
       <c r="B65" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>136141768</v>
       </c>
       <c r="B66" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>136141752</v>
       </c>
       <c r="B67" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
